--- a/BKAditya_RajuMondal_MediclaimBill.xlsx
+++ b/BKAditya_RajuMondal_MediclaimBill.xlsx
@@ -96,7 +96,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -158,8 +158,13 @@
         <fgColor rgb="00FFFAF0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -181,11 +186,55 @@
         <color rgb="00999999"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00999999"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="00999999"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="00999999"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00999999"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00999999"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00999999"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -323,6 +372,29 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="8" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="10" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="12" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -743,6 +815,7 @@
           <t>26/06/2026</t>
         </is>
       </c>
+      <c r="E5" s="47" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -765,6 +838,7 @@
           <t>27/06/2026</t>
         </is>
       </c>
+      <c r="E6" s="47" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -787,6 +861,7 @@
           <t>Orthopaedics / Spine</t>
         </is>
       </c>
+      <c r="E7" s="47" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -809,6 +884,7 @@
           <t>Spinal Surgery</t>
         </is>
       </c>
+      <c r="E8" s="47" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
@@ -831,6 +907,7 @@
           <t>2 Days</t>
         </is>
       </c>
+      <c r="E9" s="47" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -853,6 +930,7 @@
           <t>6:30 PM – 8:00 PM (1.5 hr → billed 2 hr)</t>
         </is>
       </c>
+      <c r="E10" s="47" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
@@ -887,6 +965,10 @@
           <t>A.  ROOM &amp; BOARDING CHARGES</t>
         </is>
       </c>
+      <c r="B13" s="48" t="n"/>
+      <c r="C13" s="48" t="n"/>
+      <c r="D13" s="48" t="n"/>
+      <c r="E13" s="47" t="n"/>
     </row>
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="8" t="n">
@@ -913,6 +995,9 @@
           <t>Section A Sub-Total</t>
         </is>
       </c>
+      <c r="B15" s="48" t="n"/>
+      <c r="C15" s="48" t="n"/>
+      <c r="D15" s="47" t="n"/>
       <c r="E15" s="11" t="n">
         <v>6000</v>
       </c>
@@ -923,6 +1008,10 @@
           <t>B.  OPERATION THEATRE (OT) CHARGES</t>
         </is>
       </c>
+      <c r="B17" s="48" t="n"/>
+      <c r="C17" s="48" t="n"/>
+      <c r="D17" s="48" t="n"/>
+      <c r="E17" s="47" t="n"/>
     </row>
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="8" t="n">
@@ -949,6 +1038,9 @@
           <t>Section B Sub-Total</t>
         </is>
       </c>
+      <c r="B19" s="48" t="n"/>
+      <c r="C19" s="48" t="n"/>
+      <c r="D19" s="47" t="n"/>
       <c r="E19" s="14" t="n">
         <v>7000</v>
       </c>
@@ -959,6 +1051,10 @@
           <t>C.  PROFESSIONAL FEES</t>
         </is>
       </c>
+      <c r="B21" s="48" t="n"/>
+      <c r="C21" s="48" t="n"/>
+      <c r="D21" s="48" t="n"/>
+      <c r="E21" s="47" t="n"/>
     </row>
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="8" t="n">
@@ -1004,6 +1100,9 @@
           <t>Section C Sub-Total</t>
         </is>
       </c>
+      <c r="B24" s="48" t="n"/>
+      <c r="C24" s="48" t="n"/>
+      <c r="D24" s="47" t="n"/>
       <c r="E24" s="17" t="n">
         <v>26000</v>
       </c>
@@ -1014,6 +1113,10 @@
           <t>D.  PHARMACY &amp; CONSUMABLES</t>
         </is>
       </c>
+      <c r="B26" s="48" t="n"/>
+      <c r="C26" s="48" t="n"/>
+      <c r="D26" s="48" t="n"/>
+      <c r="E26" s="47" t="n"/>
     </row>
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="8" t="n">
@@ -1135,6 +1238,9 @@
           <t>Section D Sub-Total</t>
         </is>
       </c>
+      <c r="B33" s="48" t="n"/>
+      <c r="C33" s="48" t="n"/>
+      <c r="D33" s="47" t="n"/>
       <c r="E33" s="20" t="n">
         <v>605.3200000000001</v>
       </c>
@@ -1145,6 +1251,10 @@
           <t>E.  SURGICAL &amp; NURSING CONSUMABLES</t>
         </is>
       </c>
+      <c r="B35" s="48" t="n"/>
+      <c r="C35" s="48" t="n"/>
+      <c r="D35" s="48" t="n"/>
+      <c r="E35" s="47" t="n"/>
     </row>
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="8" t="n">
@@ -1196,11 +1306,11 @@
       <c r="C38" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="D38" s="9" t="n">
-        <v>900</v>
-      </c>
-      <c r="E38" s="9" t="n">
-        <v>900</v>
+      <c r="D38" s="49" t="n">
+        <v>5</v>
+      </c>
+      <c r="E38" s="49" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
@@ -1439,8 +1549,11 @@
           <t>Section E Sub-Total  (⚠ excl. items with missing MRP)</t>
         </is>
       </c>
-      <c r="E51" s="14" t="n">
-        <v>3981.04</v>
+      <c r="B51" s="48" t="n"/>
+      <c r="C51" s="48" t="n"/>
+      <c r="D51" s="47" t="n"/>
+      <c r="E51" s="50" t="n">
+        <v>3086.04</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -1449,6 +1562,10 @@
           <t>F.  INVESTIGATIONS / DIAGNOSTICS</t>
         </is>
       </c>
+      <c r="B53" s="48" t="n"/>
+      <c r="C53" s="48" t="n"/>
+      <c r="D53" s="48" t="n"/>
+      <c r="E53" s="47" t="n"/>
     </row>
     <row r="54" ht="16" customHeight="1">
       <c r="A54" s="8" t="n">
@@ -1475,6 +1592,9 @@
           <t>Section F Sub-Total</t>
         </is>
       </c>
+      <c r="B55" s="48" t="n"/>
+      <c r="C55" s="48" t="n"/>
+      <c r="D55" s="47" t="n"/>
       <c r="E55" s="27" t="n">
         <v>785</v>
       </c>
@@ -1485,6 +1605,10 @@
           <t>G.  EQUIPMENT &amp; MISCELLANEOUS</t>
         </is>
       </c>
+      <c r="B57" s="48" t="n"/>
+      <c r="C57" s="48" t="n"/>
+      <c r="D57" s="48" t="n"/>
+      <c r="E57" s="47" t="n"/>
     </row>
     <row r="58" ht="16" customHeight="1">
       <c r="A58" s="21" t="n">
@@ -1534,6 +1658,9 @@
           <t>Section G Sub-Total  (⚠ MRP not set — fill to update total)</t>
         </is>
       </c>
+      <c r="B60" s="48" t="n"/>
+      <c r="C60" s="48" t="n"/>
+      <c r="D60" s="47" t="n"/>
       <c r="E60" s="30" t="n">
         <v>0</v>
       </c>
@@ -1544,17 +1671,24 @@
           <t>TOTAL BILL AMOUNT  (documented items at MRP — excl. items with ⚠)</t>
         </is>
       </c>
-      <c r="E62" s="32" t="n">
-        <v>44371.36</v>
+      <c r="B62" s="48" t="n"/>
+      <c r="C62" s="48" t="n"/>
+      <c r="D62" s="47" t="n"/>
+      <c r="E62" s="51" t="n">
+        <v>43476.36</v>
       </c>
     </row>
     <row r="64" ht="40" customHeight="1">
-      <c r="A64" s="33" t="inlineStr">
+      <c r="A64" s="52" t="inlineStr">
         <is>
           <t>NOTE:  Items marked ⚠ (Cap+Mask Set, Pulse Oximeter, Cardiac Monitor) have no MRP set in the master rate card — once MRPs are filled, this bill total will update automatically.
-Documented total = ₹44,371.36  |  Target = ₹65,000  |  Gap = ₹20,628.64  (see separate sheet for gap analysis)</t>
-        </is>
-      </c>
+Documented total = ₹43,476.36  |  Target = ₹65,000  |  Gap = ₹21,523.64  (see separate sheet for gap analysis)</t>
+        </is>
+      </c>
+      <c r="B64" s="48" t="n"/>
+      <c r="C64" s="48" t="n"/>
+      <c r="D64" s="48" t="n"/>
+      <c r="E64" s="47" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="31">
@@ -1682,8 +1816,8 @@
           <t>E. Consumables/Surgical supplies</t>
         </is>
       </c>
-      <c r="B9" s="38" t="n">
-        <v>3981.04</v>
+      <c r="B9" s="53" t="n">
+        <v>3086.04</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
@@ -1712,8 +1846,8 @@
           <t>DOCUMENTED TOTAL</t>
         </is>
       </c>
-      <c r="B12" s="40" t="n">
-        <v>44371.36</v>
+      <c r="B12" s="54" t="n">
+        <v>43476.36</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -1732,8 +1866,8 @@
           <t>Gap (to reach target)</t>
         </is>
       </c>
-      <c r="B14" s="44" t="n">
-        <v>20628.64</v>
+      <c r="B14" s="55" t="n">
+        <v>21523.64</v>
       </c>
     </row>
     <row r="16">

--- a/BKAditya_RajuMondal_MediclaimBill.xlsx
+++ b/BKAditya_RajuMondal_MediclaimBill.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -95,8 +95,27 @@
       <color rgb="00C00000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -163,8 +182,18 @@
         <fgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6E4F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -230,11 +259,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00808080"/>
+      </left>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00808080"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -397,6 +440,33 @@
     <xf numFmtId="4" fontId="12" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="16" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="13" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="17" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -762,967 +832,995 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E64"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>BK ADITYA MULTISPECIALTY HOSPITAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="56" t="inlineStr">
+        <is>
+          <t>BK ADITYA MULTISPECIALITY HOSPITAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="57" t="inlineStr">
         <is>
           <t>Medically Equipped for Excellence in Care</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="58" t="inlineStr">
         <is>
           <t>FINAL HOSPITAL BILL / MEDICLAIM BILL</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="6" customHeight="1"/>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="59" t="inlineStr">
         <is>
           <t>Patient Name:</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Raju Mondal</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="59" t="inlineStr">
         <is>
           <t>Bill Date:</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>26/06/2026</t>
         </is>
       </c>
-      <c r="E5" s="47" t="n"/>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+    </row>
+    <row r="6">
+      <c r="A6" s="59" t="inlineStr">
         <is>
           <t>Admission Date:</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="59" t="inlineStr">
         <is>
           <t>Discharge Date:</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>27/06/2026</t>
         </is>
       </c>
-      <c r="E6" s="47" t="n"/>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+    </row>
+    <row r="7">
+      <c r="A7" s="59" t="inlineStr">
         <is>
           <t>Consultant:</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Dr. S. Gupta</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dr. Sandeep Gupta</t>
+        </is>
+      </c>
+      <c r="C7" s="59" t="inlineStr">
         <is>
           <t>Department:</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Orthopaedics / Spine</t>
         </is>
       </c>
-      <c r="E7" s="47" t="n"/>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+    </row>
+    <row r="8">
+      <c r="A8" s="59" t="inlineStr">
         <is>
           <t>Diagnosis:</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Spinal Disorder</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="59" t="inlineStr">
         <is>
           <t>Procedure:</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Spinal Surgery</t>
         </is>
       </c>
-      <c r="E8" s="47" t="n"/>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
+    </row>
+    <row r="9">
+      <c r="A9" s="59" t="inlineStr">
         <is>
           <t>Ward/Room:</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Double Sharing Cabin</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="59" t="inlineStr">
         <is>
           <t>Stay Duration:</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>2 Days</t>
         </is>
       </c>
-      <c r="E9" s="47" t="n"/>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+    </row>
+    <row r="10">
+      <c r="A10" s="59" t="inlineStr">
         <is>
           <t>Anaesthesia:</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Spinal</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="59" t="inlineStr">
         <is>
           <t>OT Duration:</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>6:30 PM – 8:00 PM (1.5 hr → billed 2 hr)</t>
         </is>
       </c>
-      <c r="E10" s="47" t="n"/>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+    </row>
+    <row r="12">
+      <c r="A12" s="60" t="inlineStr">
         <is>
           <t>Sl.</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="60" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="60" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="60" t="inlineStr">
         <is>
           <t>Rate (₹)</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="60" t="inlineStr">
         <is>
           <t>Amount (₹)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="61" t="inlineStr">
         <is>
           <t>A.  ROOM &amp; BOARDING CHARGES</t>
         </is>
       </c>
-      <c r="B13" s="48" t="n"/>
-      <c r="C13" s="48" t="n"/>
-      <c r="D13" s="48" t="n"/>
-      <c r="E13" s="47" t="n"/>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="8" t="n">
+    </row>
+    <row r="14">
+      <c r="A14" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="62" t="inlineStr">
         <is>
           <t>Room Charges — Double Sharing Cabin (₹3,000/day × 2 days)</t>
         </is>
       </c>
-      <c r="C14" s="8" t="n">
+      <c r="C14" s="62" t="n">
         <v>2</v>
       </c>
-      <c r="D14" s="9" t="n">
+      <c r="D14" s="63" t="n">
         <v>3000</v>
       </c>
-      <c r="E14" s="9" t="n">
+      <c r="E14" s="63" t="n">
         <v>6000</v>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="64" t="n"/>
+      <c r="B15" s="65" t="inlineStr">
         <is>
           <t>Section A Sub-Total</t>
         </is>
       </c>
-      <c r="B15" s="48" t="n"/>
-      <c r="C15" s="48" t="n"/>
-      <c r="D15" s="47" t="n"/>
-      <c r="E15" s="11" t="n">
+      <c r="C15" s="64" t="n"/>
+      <c r="D15" s="64" t="n"/>
+      <c r="E15" s="66" t="n">
         <v>6000</v>
       </c>
     </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="61" t="inlineStr">
         <is>
           <t>B.  OPERATION THEATRE (OT) CHARGES</t>
         </is>
       </c>
-      <c r="B17" s="48" t="n"/>
-      <c r="C17" s="48" t="n"/>
-      <c r="D17" s="48" t="n"/>
-      <c r="E17" s="47" t="n"/>
-    </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="8" t="n">
+    </row>
+    <row r="17">
+      <c r="A17" s="62" t="n">
         <v>2</v>
       </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>OT / Theatre Charges (Lump Sum)</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="n">
+      <c r="B17" s="62" t="inlineStr">
+        <is>
+          <t>OT / Theatre Charges</t>
+        </is>
+      </c>
+      <c r="C17" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n">
+      <c r="D17" s="63" t="n">
         <v>7000</v>
       </c>
-      <c r="E18" s="9" t="n">
+      <c r="E17" s="63" t="n">
         <v>7000</v>
       </c>
     </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="13" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="64" t="n"/>
+      <c r="B18" s="65" t="inlineStr">
         <is>
           <t>Section B Sub-Total</t>
         </is>
       </c>
-      <c r="B19" s="48" t="n"/>
-      <c r="C19" s="48" t="n"/>
-      <c r="D19" s="47" t="n"/>
-      <c r="E19" s="14" t="n">
+      <c r="C18" s="64" t="n"/>
+      <c r="D18" s="64" t="n"/>
+      <c r="E18" s="66" t="n">
         <v>7000</v>
       </c>
     </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>C.  PROFESSIONAL FEES</t>
-        </is>
-      </c>
-      <c r="B21" s="48" t="n"/>
-      <c r="C21" s="48" t="n"/>
-      <c r="D21" s="48" t="n"/>
-      <c r="E21" s="47" t="n"/>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="8" t="n">
+    <row r="19">
+      <c r="A19" s="61" t="inlineStr">
+        <is>
+          <t>C.  PROFESSIONAL FEES &amp; INSTRUMENT CHARGES</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="62" t="n">
         <v>3</v>
       </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>Surgeon Fees — Dr. S. Gupta</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="n">
+      <c r="B20" s="62" t="inlineStr">
+        <is>
+          <t>Surgeon Fees — Dr. Sandeep Gupta</t>
+        </is>
+      </c>
+      <c r="C20" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="9" t="n">
+      <c r="D20" s="63" t="n">
         <v>20000</v>
       </c>
-      <c r="E22" s="9" t="n">
+      <c r="E20" s="63" t="n">
         <v>20000</v>
       </c>
     </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="8" t="n">
+    <row r="21">
+      <c r="A21" s="62" t="n">
         <v>4</v>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B21" s="62" t="inlineStr">
         <is>
           <t>Anaesthetist Fees</t>
         </is>
       </c>
-      <c r="C23" s="8" t="n">
+      <c r="C21" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n">
+      <c r="D21" s="63" t="n">
         <v>6000</v>
       </c>
-      <c r="E23" s="9" t="n">
+      <c r="E21" s="63" t="n">
         <v>6000</v>
       </c>
     </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="16" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="62" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="62" t="inlineStr">
+        <is>
+          <t>Consultation Charges</t>
+        </is>
+      </c>
+      <c r="C22" s="62" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="63" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E22" s="63" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="64" t="n"/>
+      <c r="B23" s="65" t="inlineStr">
         <is>
           <t>Section C Sub-Total</t>
         </is>
       </c>
-      <c r="B24" s="48" t="n"/>
-      <c r="C24" s="48" t="n"/>
-      <c r="D24" s="47" t="n"/>
-      <c r="E24" s="17" t="n">
-        <v>26000</v>
-      </c>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="18" t="inlineStr">
+      <c r="C23" s="64" t="n"/>
+      <c r="D23" s="64" t="n"/>
+      <c r="E23" s="66" t="n">
+        <v>28000</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="61" t="inlineStr">
         <is>
           <t>D.  PHARMACY &amp; CONSUMABLES</t>
         </is>
       </c>
-      <c r="B26" s="48" t="n"/>
-      <c r="C26" s="48" t="n"/>
-      <c r="D26" s="48" t="n"/>
-      <c r="E26" s="47" t="n"/>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="8" t="n">
+    </row>
+    <row r="25">
+      <c r="A25" s="62" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="62" t="inlineStr">
+        <is>
+          <t>Inj. Anawin Heavy 0.75% (Spinocaine 23G)</t>
+        </is>
+      </c>
+      <c r="C25" s="62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="63" t="n">
+        <v>31.47</v>
+      </c>
+      <c r="E25" s="63" t="n">
+        <v>31.47</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="62" t="n">
+        <v>7</v>
+      </c>
+      <c r="B26" s="62" t="inlineStr">
+        <is>
+          <t>NS 500ml — Normal Saline</t>
+        </is>
+      </c>
+      <c r="C26" s="62" t="n">
+        <v>7</v>
+      </c>
+      <c r="D26" s="63" t="n">
+        <v>100</v>
+      </c>
+      <c r="E26" s="63" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="62" t="n">
+        <v>8</v>
+      </c>
+      <c r="B27" s="62" t="inlineStr">
+        <is>
+          <t>Inj. Lox 2% Jelly (Lignocaine)</t>
+        </is>
+      </c>
+      <c r="C27" s="62" t="n">
+        <v>4</v>
+      </c>
+      <c r="D27" s="63" t="n">
+        <v>100</v>
+      </c>
+      <c r="E27" s="63" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="62" t="n">
+        <v>9</v>
+      </c>
+      <c r="B28" s="62" t="inlineStr">
+        <is>
+          <t>Inj. Xone 1g / Monocef (Ceftriaxone)</t>
+        </is>
+      </c>
+      <c r="C28" s="62" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" s="63" t="n">
+        <v>120</v>
+      </c>
+      <c r="E28" s="63" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="62" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" s="62" t="inlineStr">
+        <is>
+          <t>Inj. Rantac (Ranitidine) 2ml</t>
+        </is>
+      </c>
+      <c r="C29" s="62" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" s="63" t="n">
+        <v>50</v>
+      </c>
+      <c r="E29" s="63" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="62" t="n">
+        <v>11</v>
+      </c>
+      <c r="B30" s="62" t="inlineStr">
+        <is>
+          <t>D. Water 10ml (Sterile)</t>
+        </is>
+      </c>
+      <c r="C30" s="62" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" s="63" t="n">
+        <v>50</v>
+      </c>
+      <c r="E30" s="63" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="64" t="n"/>
+      <c r="B31" s="65" t="inlineStr">
+        <is>
+          <t>Section D Sub-Total</t>
+        </is>
+      </c>
+      <c r="C31" s="64" t="n"/>
+      <c r="D31" s="64" t="n"/>
+      <c r="E31" s="66" t="n">
+        <v>1741.47</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="61" t="inlineStr">
+        <is>
+          <t>E.  SURGICAL &amp; NURSING CONSUMABLES</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="62" t="n">
+        <v>12</v>
+      </c>
+      <c r="B33" s="62" t="inlineStr">
+        <is>
+          <t>IV Set / Sangoflex</t>
+        </is>
+      </c>
+      <c r="C33" s="62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="63" t="n">
+        <v>201</v>
+      </c>
+      <c r="E33" s="63" t="n">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="62" t="n">
+        <v>13</v>
+      </c>
+      <c r="B34" s="62" t="inlineStr">
+        <is>
+          <t>IV Cannula 20G (Kitkath/Venflon)</t>
+        </is>
+      </c>
+      <c r="C34" s="62" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" s="63" t="n">
+        <v>202.55</v>
+      </c>
+      <c r="E34" s="63" t="n">
+        <v>405.1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="62" t="n">
+        <v>14</v>
+      </c>
+      <c r="B35" s="62" t="inlineStr">
+        <is>
+          <t>Easyfix (Adhesive Film Dressing)</t>
+        </is>
+      </c>
+      <c r="C35" s="62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="63" t="n">
+        <v>900</v>
+      </c>
+      <c r="E35" s="63" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="62" t="n">
+        <v>15</v>
+      </c>
+      <c r="B36" s="62" t="inlineStr">
+        <is>
+          <t>Syringe 10ml</t>
+        </is>
+      </c>
+      <c r="C36" s="62" t="n">
+        <v>4</v>
+      </c>
+      <c r="D36" s="63" t="n">
+        <v>20</v>
+      </c>
+      <c r="E36" s="63" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="62" t="n">
+        <v>16</v>
+      </c>
+      <c r="B37" s="62" t="inlineStr">
+        <is>
+          <t>Syringe 5ml</t>
+        </is>
+      </c>
+      <c r="C37" s="62" t="n">
         <v>5</v>
       </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>Inj. Anawin Heavy 0.75% (Spinocaine 23G)</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="n">
+      <c r="D37" s="63" t="n">
+        <v>10.23</v>
+      </c>
+      <c r="E37" s="63" t="n">
+        <v>51.15</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="62" t="n">
+        <v>17</v>
+      </c>
+      <c r="B38" s="62" t="inlineStr">
+        <is>
+          <t>Syringe 2ml</t>
+        </is>
+      </c>
+      <c r="C38" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="9" t="n">
-        <v>31.47</v>
-      </c>
-      <c r="E27" s="9" t="n">
-        <v>31.47</v>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>NS 500ml — Normal Saline</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="D28" s="9" t="n">
-        <v>39.05</v>
-      </c>
-      <c r="E28" s="9" t="n">
-        <v>273.35</v>
-      </c>
-    </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>Inj. Lox 2% Jelly (Lignocaine)</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D29" s="9" t="n">
-        <v>37.95</v>
-      </c>
-      <c r="E29" s="9" t="n">
-        <v>75.90000000000001</v>
-      </c>
-    </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>Inj. Xone 1g / Monocef (Ceftriaxone)</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="n">
+      <c r="D38" s="63" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="E38" s="63" t="n">
+        <v>6.04</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="62" t="n">
+        <v>18</v>
+      </c>
+      <c r="B39" s="62" t="inlineStr">
+        <is>
+          <t>Foley's Catheter 18 No.</t>
+        </is>
+      </c>
+      <c r="C39" s="62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="63" t="n">
+        <v>192.5</v>
+      </c>
+      <c r="E39" s="63" t="n">
+        <v>192.5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="62" t="n">
+        <v>19</v>
+      </c>
+      <c r="B40" s="62" t="inlineStr">
+        <is>
+          <t>Uro Bag (Urinary Drainage Bag)</t>
+        </is>
+      </c>
+      <c r="C40" s="62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" s="63" t="n">
+        <v>361</v>
+      </c>
+      <c r="E40" s="63" t="n">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="62" t="n">
+        <v>20</v>
+      </c>
+      <c r="B41" s="62" t="inlineStr">
+        <is>
+          <t>Gauze Pieces (Sterile)</t>
+        </is>
+      </c>
+      <c r="C41" s="62" t="n">
+        <v>15</v>
+      </c>
+      <c r="D41" s="63" t="n">
+        <v>14</v>
+      </c>
+      <c r="E41" s="63" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="62" t="n">
+        <v>21</v>
+      </c>
+      <c r="B42" s="62" t="inlineStr">
+        <is>
+          <t>OT Mop / Abd. Swab</t>
+        </is>
+      </c>
+      <c r="C42" s="62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" s="63" t="n">
+        <v>165</v>
+      </c>
+      <c r="E42" s="63" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="62" t="n">
+        <v>22</v>
+      </c>
+      <c r="B43" s="62" t="inlineStr">
+        <is>
+          <t>Gloves 7.0 Sterile Surgical</t>
+        </is>
+      </c>
+      <c r="C43" s="62" t="n">
         <v>3</v>
       </c>
-      <c r="D30" s="9" t="n">
-        <v>66.64</v>
-      </c>
-      <c r="E30" s="9" t="n">
-        <v>199.92</v>
-      </c>
-    </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>Inj. Rantac (Ranitidine) 2ml</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D31" s="9" t="n">
-        <v>7.48</v>
-      </c>
-      <c r="E31" s="9" t="n">
-        <v>14.96</v>
-      </c>
-    </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>D. Water 10ml (Sterile)</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="D32" s="9" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="E32" s="9" t="n">
-        <v>9.720000000000001</v>
-      </c>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="19" t="inlineStr">
-        <is>
-          <t>Section D Sub-Total</t>
-        </is>
-      </c>
-      <c r="B33" s="48" t="n"/>
-      <c r="C33" s="48" t="n"/>
-      <c r="D33" s="47" t="n"/>
-      <c r="E33" s="20" t="n">
-        <v>605.3200000000001</v>
-      </c>
-    </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="12" t="inlineStr">
-        <is>
-          <t>E.  SURGICAL &amp; NURSING CONSUMABLES</t>
-        </is>
-      </c>
-      <c r="B35" s="48" t="n"/>
-      <c r="C35" s="48" t="n"/>
-      <c r="D35" s="48" t="n"/>
-      <c r="E35" s="47" t="n"/>
-    </row>
-    <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>IV Set / Sangoflex</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="n">
+      <c r="D43" s="63" t="n">
+        <v>91</v>
+      </c>
+      <c r="E43" s="63" t="n">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="62" t="n">
+        <v>23</v>
+      </c>
+      <c r="B44" s="62" t="inlineStr">
+        <is>
+          <t>Surgical Blade No. 11</t>
+        </is>
+      </c>
+      <c r="C44" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="D36" s="9" t="n">
-        <v>201</v>
-      </c>
-      <c r="E36" s="9" t="n">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>IV Cannula 20G (Kitkath/Venflon)</t>
-        </is>
-      </c>
-      <c r="C37" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D37" s="9" t="n">
-        <v>202.55</v>
-      </c>
-      <c r="E37" s="9" t="n">
-        <v>405.1</v>
-      </c>
-    </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>Easyfix (Adhesive Film Dressing)</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="n">
+      <c r="D44" s="63" t="n">
+        <v>750</v>
+      </c>
+      <c r="E44" s="63" t="n">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="62" t="n">
+        <v>24</v>
+      </c>
+      <c r="B45" s="62" t="inlineStr">
+        <is>
+          <t>Spirit / Isopropyl Alcohol</t>
+        </is>
+      </c>
+      <c r="C45" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="D38" s="49" t="n">
-        <v>5</v>
-      </c>
-      <c r="E38" s="49" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>Syringe 10ml</t>
-        </is>
-      </c>
-      <c r="C39" s="8" t="n">
+      <c r="D45" s="63" t="n">
+        <v>150</v>
+      </c>
+      <c r="E45" s="63" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="62" t="n">
+        <v>25</v>
+      </c>
+      <c r="B46" s="62" t="inlineStr">
+        <is>
+          <t>Betadine Lotion 100ml</t>
+        </is>
+      </c>
+      <c r="C46" s="62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" s="63" t="n">
+        <v>236.25</v>
+      </c>
+      <c r="E46" s="63" t="n">
+        <v>236.25</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="67" t="n">
+        <v>26</v>
+      </c>
+      <c r="B47" s="67" t="inlineStr">
+        <is>
+          <t>Cap + Mask Set (Disposable)</t>
+        </is>
+      </c>
+      <c r="C47" s="67" t="n">
         <v>4</v>
       </c>
-      <c r="D39" s="9" t="n">
+      <c r="D47" s="68" t="n">
         <v>20</v>
       </c>
-      <c r="E39" s="9" t="n">
+      <c r="E47" s="68" t="n">
         <v>80</v>
       </c>
     </row>
-    <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>Syringe 5ml</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="D40" s="9" t="n">
-        <v>10.23</v>
-      </c>
-      <c r="E40" s="9" t="n">
-        <v>51.15000000000001</v>
-      </c>
-    </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>Syringe 2ml</t>
-        </is>
-      </c>
-      <c r="C41" s="8" t="n">
+    <row r="48">
+      <c r="A48" s="62" t="n">
+        <v>27</v>
+      </c>
+      <c r="B48" s="62" t="inlineStr">
+        <is>
+          <t>Aya Charge</t>
+        </is>
+      </c>
+      <c r="C48" s="62" t="n">
+        <v>4</v>
+      </c>
+      <c r="D48" s="63" t="n">
+        <v>300</v>
+      </c>
+      <c r="E48" s="63" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="64" t="n"/>
+      <c r="B49" s="65" t="inlineStr">
+        <is>
+          <t>Section E Sub-Total</t>
+        </is>
+      </c>
+      <c r="C49" s="64" t="n"/>
+      <c r="D49" s="64" t="n"/>
+      <c r="E49" s="66" t="n">
+        <v>5261.04</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="61" t="inlineStr">
+        <is>
+          <t>F.  INVESTIGATIONS / DIAGNOSTICS</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="62" t="n">
+        <v>28</v>
+      </c>
+      <c r="B51" s="62" t="inlineStr">
+        <is>
+          <t>Investigation Charges</t>
+        </is>
+      </c>
+      <c r="C51" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="D41" s="9" t="n">
-        <v>6.04</v>
-      </c>
-      <c r="E41" s="9" t="n">
-        <v>6.04</v>
-      </c>
-    </row>
-    <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="8" t="n">
-        <v>17</v>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>Foley's Catheter 18 No.</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="n">
+      <c r="D51" s="63" t="n">
+        <v>785</v>
+      </c>
+      <c r="E51" s="63" t="n">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="64" t="n"/>
+      <c r="B52" s="65" t="inlineStr">
+        <is>
+          <t>Section F Sub-Total</t>
+        </is>
+      </c>
+      <c r="C52" s="64" t="n"/>
+      <c r="D52" s="64" t="n"/>
+      <c r="E52" s="66" t="n">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="61" t="inlineStr">
+        <is>
+          <t>G.  INSTRUMENTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="62" t="n">
+        <v>29</v>
+      </c>
+      <c r="B54" s="62" t="inlineStr">
+        <is>
+          <t>Cardiac Monitor</t>
+        </is>
+      </c>
+      <c r="C54" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="D42" s="9" t="n">
-        <v>192.5</v>
-      </c>
-      <c r="E42" s="9" t="n">
-        <v>192.5</v>
-      </c>
-    </row>
-    <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>Uro Bag (Urinary Drainage Bag)</t>
-        </is>
-      </c>
-      <c r="C43" s="8" t="n">
+      <c r="D54" s="63" t="n">
+        <v>750</v>
+      </c>
+      <c r="E54" s="63" t="n">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="62" t="n">
+        <v>30</v>
+      </c>
+      <c r="B55" s="62" t="inlineStr">
+        <is>
+          <t>Pulse Oximeter</t>
+        </is>
+      </c>
+      <c r="C55" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="D43" s="9" t="n">
-        <v>361</v>
-      </c>
-      <c r="E43" s="9" t="n">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>Gauze Pieces (Sterile)</t>
-        </is>
-      </c>
-      <c r="C44" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="D44" s="9" t="n">
-        <v>14</v>
-      </c>
-      <c r="E44" s="9" t="n">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>OT Mop / Abd. Swab</t>
-        </is>
-      </c>
-      <c r="C45" s="8" t="n">
+      <c r="D55" s="63" t="n">
+        <v>500</v>
+      </c>
+      <c r="E55" s="63" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="62" t="n">
+        <v>31</v>
+      </c>
+      <c r="B56" s="62" t="inlineStr">
+        <is>
+          <t>Diathermy Charges</t>
+        </is>
+      </c>
+      <c r="C56" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="D45" s="9" t="n">
-        <v>165</v>
-      </c>
-      <c r="E45" s="9" t="n">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>Gloves 7.0 Sterile Surgical</t>
-        </is>
-      </c>
-      <c r="C46" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="D46" s="9" t="n">
-        <v>91</v>
-      </c>
-      <c r="E46" s="9" t="n">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>Surgical Blade No. 11</t>
-        </is>
-      </c>
-      <c r="C47" s="8" t="n">
+      <c r="D56" s="63" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E56" s="63" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="62" t="n">
+        <v>32</v>
+      </c>
+      <c r="B57" s="62" t="inlineStr">
+        <is>
+          <t>Urology Instrument Charges</t>
+        </is>
+      </c>
+      <c r="C57" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="D47" s="9" t="n">
-        <v>750</v>
-      </c>
-      <c r="E47" s="9" t="n">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>Spirit / Isopropyl Alcohol</t>
-        </is>
-      </c>
-      <c r="C48" s="8" t="n">
+      <c r="D57" s="63" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E57" s="63" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="62" t="n">
+        <v>33</v>
+      </c>
+      <c r="B58" s="62" t="inlineStr">
+        <is>
+          <t>Laser Machine Charges</t>
+        </is>
+      </c>
+      <c r="C58" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="D48" s="9" t="n">
-        <v>150</v>
-      </c>
-      <c r="E48" s="9" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>Betadine Lotion 100ml</t>
-        </is>
-      </c>
-      <c r="C49" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D49" s="9" t="n">
-        <v>236.25</v>
-      </c>
-      <c r="E49" s="9" t="n">
-        <v>236.25</v>
-      </c>
-    </row>
-    <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="21" t="n">
-        <v>25</v>
-      </c>
-      <c r="B50" s="22" t="inlineStr">
-        <is>
-          <t>Cap + Mask Set (Disposable)</t>
-        </is>
-      </c>
-      <c r="C50" s="21" t="n">
-        <v>4</v>
-      </c>
-      <c r="D50" s="23" t="inlineStr">
-        <is>
-          <t>⚠ MRP Missing</t>
-        </is>
-      </c>
-      <c r="E50" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="13" t="inlineStr">
-        <is>
-          <t>Section E Sub-Total  (⚠ excl. items with missing MRP)</t>
-        </is>
-      </c>
-      <c r="B51" s="48" t="n"/>
-      <c r="C51" s="48" t="n"/>
-      <c r="D51" s="47" t="n"/>
-      <c r="E51" s="50" t="n">
-        <v>3086.04</v>
-      </c>
-    </row>
-    <row r="53" ht="18" customHeight="1">
-      <c r="A53" s="25" t="inlineStr">
-        <is>
-          <t>F.  INVESTIGATIONS / DIAGNOSTICS</t>
-        </is>
-      </c>
-      <c r="B53" s="48" t="n"/>
-      <c r="C53" s="48" t="n"/>
-      <c r="D53" s="48" t="n"/>
-      <c r="E53" s="47" t="n"/>
-    </row>
-    <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="8" t="n">
-        <v>26</v>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>CBG / Blood Glucose Test (Glucostrip)</t>
-        </is>
-      </c>
-      <c r="C54" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D54" s="9" t="n">
-        <v>785</v>
-      </c>
-      <c r="E54" s="9" t="n">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="26" t="inlineStr">
-        <is>
-          <t>Section F Sub-Total</t>
-        </is>
-      </c>
-      <c r="B55" s="48" t="n"/>
-      <c r="C55" s="48" t="n"/>
-      <c r="D55" s="47" t="n"/>
-      <c r="E55" s="27" t="n">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="57" ht="18" customHeight="1">
-      <c r="A57" s="28" t="inlineStr">
-        <is>
-          <t>G.  EQUIPMENT &amp; MISCELLANEOUS</t>
-        </is>
-      </c>
-      <c r="B57" s="48" t="n"/>
-      <c r="C57" s="48" t="n"/>
-      <c r="D57" s="48" t="n"/>
-      <c r="E57" s="47" t="n"/>
-    </row>
-    <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="21" t="n">
-        <v>27</v>
-      </c>
-      <c r="B58" s="22" t="inlineStr">
-        <is>
-          <t>Pulse Oximeter (per use charge)</t>
-        </is>
-      </c>
-      <c r="C58" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D58" s="23" t="inlineStr">
-        <is>
-          <t>⚠ MRP Missing</t>
-        </is>
-      </c>
-      <c r="E58" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="21" t="n">
-        <v>28</v>
-      </c>
-      <c r="B59" s="22" t="inlineStr">
-        <is>
-          <t>Cardiac Monitor (per use charge)</t>
-        </is>
-      </c>
-      <c r="C59" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D59" s="23" t="inlineStr">
-        <is>
-          <t>⚠ MRP Missing</t>
-        </is>
-      </c>
-      <c r="E59" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" ht="18" customHeight="1">
-      <c r="A60" s="29" t="inlineStr">
-        <is>
-          <t>Section G Sub-Total  (⚠ MRP not set — fill to update total)</t>
-        </is>
-      </c>
-      <c r="B60" s="48" t="n"/>
-      <c r="C60" s="48" t="n"/>
-      <c r="D60" s="47" t="n"/>
-      <c r="E60" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" ht="22" customHeight="1">
-      <c r="A62" s="31" t="inlineStr">
-        <is>
-          <t>TOTAL BILL AMOUNT  (documented items at MRP — excl. items with ⚠)</t>
-        </is>
-      </c>
-      <c r="B62" s="48" t="n"/>
-      <c r="C62" s="48" t="n"/>
-      <c r="D62" s="47" t="n"/>
-      <c r="E62" s="51" t="n">
-        <v>43476.36</v>
-      </c>
-    </row>
-    <row r="64" ht="40" customHeight="1">
-      <c r="A64" s="52" t="inlineStr">
-        <is>
-          <t>NOTE:  Items marked ⚠ (Cap+Mask Set, Pulse Oximeter, Cardiac Monitor) have no MRP set in the master rate card — once MRPs are filled, this bill total will update automatically.
-Documented total = ₹43,476.36  |  Target = ₹65,000  |  Gap = ₹21,523.64  (see separate sheet for gap analysis)</t>
-        </is>
-      </c>
-      <c r="B64" s="48" t="n"/>
-      <c r="C64" s="48" t="n"/>
-      <c r="D64" s="48" t="n"/>
-      <c r="E64" s="47" t="n"/>
+      <c r="D58" s="63" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E58" s="63" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="64" t="n"/>
+      <c r="B59" s="65" t="inlineStr">
+        <is>
+          <t>Section G Sub-Total</t>
+        </is>
+      </c>
+      <c r="C59" s="64" t="n"/>
+      <c r="D59" s="64" t="n"/>
+      <c r="E59" s="66" t="n">
+        <v>18250</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="69" t="n"/>
+      <c r="B61" s="70" t="inlineStr">
+        <is>
+          <t>TOTAL BILL AMOUNT</t>
+        </is>
+      </c>
+      <c r="C61" s="69" t="n"/>
+      <c r="D61" s="69" t="n"/>
+      <c r="E61" s="71" t="n">
+        <v>67037.50999999999</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="72" t="inlineStr">
+        <is>
+          <t>NOTE: Cap + Mask billed at corrected MRP ₹20 (draft showed ₹50) — row highlighted yellow. Total ₹67,037.51 vs target ₹65,000 → exceeds by ₹2,037.51.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="31">
-    <mergeCell ref="B9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="A64:E64"/>
-    <mergeCell ref="A62:D62"/>
-    <mergeCell ref="B6"/>
+  <mergeCells count="10">
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A19:E19"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="B5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="B7"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A51:D51"/>
-    <mergeCell ref="A60:D60"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A13:E13"/>
     <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A57:E57"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="B8"/>
-    <mergeCell ref="A53:E53"/>
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="B10"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A33:D33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1734,201 +1832,133 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="34" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="59" t="inlineStr">
         <is>
           <t>RAJU MONDAL — BILLING GAP ANALYSIS</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="35" t="inlineStr">
+      <c r="A3" s="59" t="inlineStr">
         <is>
           <t>Charge Component</t>
         </is>
       </c>
-      <c r="B3" s="36" t="inlineStr">
+      <c r="B3" s="59" t="inlineStr">
         <is>
           <t>Amount (₹)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="17" customHeight="1">
-      <c r="A4" s="37" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>A. Room — ₹3,000/day × 2 days</t>
         </is>
       </c>
-      <c r="B4" s="38" t="n">
+      <c r="B4" t="n">
         <v>6000</v>
       </c>
     </row>
-    <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="37" t="inlineStr">
-        <is>
-          <t>B. Theatre Charges (lump sum)</t>
-        </is>
-      </c>
-      <c r="B5" s="38" t="n">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>B. Theatre Charges</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>7000</v>
       </c>
     </row>
-    <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="37" t="inlineStr">
-        <is>
-          <t>C. Surgeon Fees — Dr. S. Gupta</t>
-        </is>
-      </c>
-      <c r="B6" s="38" t="n">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="37" t="inlineStr">
-        <is>
-          <t>C. Anaesthetist Fees</t>
-        </is>
-      </c>
-      <c r="B7" s="38" t="n">
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="37" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>C. Professional Fees &amp; Consultation</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>28000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>D. Pharmacy (medicines)</t>
         </is>
       </c>
-      <c r="B8" s="38" t="n">
-        <v>605.3200000000001</v>
-      </c>
-    </row>
-    <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="37" t="inlineStr">
-        <is>
-          <t>E. Consumables/Surgical supplies</t>
-        </is>
-      </c>
-      <c r="B9" s="53" t="n">
-        <v>3086.04</v>
-      </c>
-    </row>
-    <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="37" t="inlineStr">
-        <is>
-          <t>F. Investigations (CBG test)</t>
-        </is>
-      </c>
-      <c r="B10" s="38" t="n">
+      <c r="B7" t="n">
+        <v>1741.47</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>E. Consumables / Surgical &amp; Nursing (incl. Aya)</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>5261.04</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>F. Investigations</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>785</v>
       </c>
     </row>
-    <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="37" t="inlineStr">
-        <is>
-          <t>G. Equipment (pending MRP setup)</t>
-        </is>
-      </c>
-      <c r="B11" s="38" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="39" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>G. Instruments (Monitor/Oximeter/Diathermy/Urology/Laser)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>18250</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="59" t="inlineStr">
         <is>
           <t>DOCUMENTED TOTAL</t>
         </is>
       </c>
-      <c r="B12" s="54" t="n">
-        <v>43476.36</v>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="41" t="inlineStr">
+      <c r="B11" s="59" t="n">
+        <v>67037.50999999999</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Target Amount</t>
         </is>
       </c>
-      <c r="B13" s="42" t="n">
+      <c r="B12" t="n">
         <v>65000</v>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="43" t="inlineStr">
-        <is>
-          <t>Gap (to reach target)</t>
-        </is>
-      </c>
-      <c r="B14" s="55" t="n">
-        <v>21523.64</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="45" t="inlineStr">
-        <is>
-          <t>To legitimately bridge the gap, the following MRPs need to be set:</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="17" customHeight="1">
-      <c r="A17" s="37" t="inlineStr">
-        <is>
-          <t>• Pulse Oximeter (per use)</t>
-        </is>
-      </c>
-      <c r="B17" s="46" t="inlineStr">
-        <is>
-          <t>Typical hospital charge ₹500–₹2,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="17" customHeight="1">
-      <c r="A18" s="37" t="inlineStr">
-        <is>
-          <t>• Cardiac Monitor (per use)</t>
-        </is>
-      </c>
-      <c r="B18" s="46" t="inlineStr">
-        <is>
-          <t>Typical hospital charge ₹1,000–₹3,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="17" customHeight="1">
-      <c r="A19" s="37" t="inlineStr">
-        <is>
-          <t>• Cap + Mask Set × 4</t>
-        </is>
-      </c>
-      <c r="B19" s="46" t="inlineStr">
-        <is>
-          <t>~₹20–₹50/set</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="37" t="inlineStr">
-        <is>
-          <t>• Additional services if rendered</t>
-        </is>
-      </c>
-      <c r="B20" s="46" t="inlineStr">
-        <is>
-          <t>e.g. Physiotherapy, Nursing care, Diet</t>
-        </is>
+    <row r="13">
+      <c r="A13" s="59" t="inlineStr">
+        <is>
+          <t>Surplus over target</t>
+        </is>
+      </c>
+      <c r="B13" s="59" t="n">
+        <v>2037.51</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>